--- a/data/trans_dic/P2A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,04; 35,56</t>
+          <t>21,22; 35,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,33; 44,13</t>
+          <t>28,46; 44,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,14; 41,79</t>
+          <t>24,62; 41,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70,65; 82,53</t>
+          <t>69,97; 82,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,74; 41,8</t>
+          <t>27,09; 41,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,72; 43,33</t>
+          <t>27,43; 43,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,76; 38,36</t>
+          <t>22,36; 38,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,73; 78,38</t>
+          <t>51,69; 77,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,03; 36,43</t>
+          <t>26,19; 36,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,1; 41,27</t>
+          <t>30,63; 41,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,63; 37,27</t>
+          <t>26,29; 37,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61,72; 78,11</t>
+          <t>62,11; 77,92</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,91; 37,78</t>
+          <t>24,33; 37,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,75; 43,75</t>
+          <t>30,25; 43,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,25; 40,54</t>
+          <t>28,13; 39,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65,25; 79,55</t>
+          <t>64,88; 78,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,04; 43,31</t>
+          <t>30,35; 43,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,44; 46,06</t>
+          <t>32,34; 45,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,49; 40,98</t>
+          <t>29,57; 41,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>68,18; 79,82</t>
+          <t>68,16; 79,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,21; 38,55</t>
+          <t>29,39; 37,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,57; 42,74</t>
+          <t>33,34; 42,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,76; 38,79</t>
+          <t>30,65; 38,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>69,23; 78,06</t>
+          <t>69,32; 78,22</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,82; 46,66</t>
+          <t>32,5; 45,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,63; 40,24</t>
+          <t>25,44; 40,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,57; 36,35</t>
+          <t>23,08; 35,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74,7; 89,11</t>
+          <t>74,94; 88,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,82; 49,45</t>
+          <t>35,52; 49,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,8; 41,85</t>
+          <t>27,06; 41,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,98; 40,37</t>
+          <t>27,78; 40,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71,45; 83,38</t>
+          <t>71,24; 82,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35,75; 45,63</t>
+          <t>35,8; 46,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,73; 38,38</t>
+          <t>28,39; 38,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27,48; 36,77</t>
+          <t>27,37; 36,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>74,7; 83,98</t>
+          <t>75,12; 84,65</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,29; 40,01</t>
+          <t>27,66; 39,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,55; 42,89</t>
+          <t>29,8; 43,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,89; 44,68</t>
+          <t>32,23; 44,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,13; 85,25</t>
+          <t>74,5; 85,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,09; 43,53</t>
+          <t>31,07; 43,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,07; 38,25</t>
+          <t>25,77; 37,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,64; 38,87</t>
+          <t>26,6; 39,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>76,47; 86,45</t>
+          <t>75,85; 86,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,03; 39,63</t>
+          <t>30,17; 39,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,34; 38,57</t>
+          <t>29,44; 38,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31,15; 39,89</t>
+          <t>31,14; 39,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,33; 84,27</t>
+          <t>76,84; 84,23</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,64; 36,33</t>
+          <t>29,7; 36,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,76; 39,16</t>
+          <t>32,1; 39,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,69; 37,3</t>
+          <t>31,04; 37,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74,65; 81,5</t>
+          <t>74,32; 81,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,89; 40,4</t>
+          <t>33,88; 40,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,81; 38,71</t>
+          <t>32,03; 38,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,28; 36,87</t>
+          <t>30,35; 36,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>71,22; 78,63</t>
+          <t>71,37; 79,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,83; 37,65</t>
+          <t>32,76; 37,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32,69; 37,54</t>
+          <t>32,85; 37,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31,33; 36,24</t>
+          <t>31,23; 35,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,89; 79,25</t>
+          <t>74,12; 79,18</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>29244</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>34642</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>29617</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>90123</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>39880</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>40360</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>31745</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>94665</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>69124</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>75001</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>61362</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>184789</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>22327; 36818</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>27644; 43336</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>22175; 37375</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82065; 96838</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>32042; 48714</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>30857; 48647</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>23401; 40107</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>72583; 109058</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>58541; 81146</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>64208; 86363</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>51208; 72975</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>160056; 200802</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>38430</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>47166</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>51320</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>140114</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>51795</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>60402</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>61947</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>190549</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>90225</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>107568</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>113268</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>330664</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>30402; 46995</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39018; 56635</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>42742; 60667</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>123606; 149885</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>42717; 60718</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>49982; 70618</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>51840; 72832</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>173820; 203007</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>78087; 100507</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>94544; 121478</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>100286; 126408</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>308843; 348504</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>42262</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34194</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>34505</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>154115</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>47541</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>39990</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>45038</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>143586</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>89802</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>74183</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>79543</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>297701</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>35054; 49575</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>26672; 42309</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>26904; 41883</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>142691; 169159</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>39980; 56231</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>31599; 48392</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>36903; 54422</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>131998; 153668</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>78909; 102015</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>62929; 84960</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>68262; 92049</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>282198; 318002</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>55700</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>53069</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>63702</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>134393</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>57994</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>48566</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>51612</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>147649</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>113695</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>101635</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>115314</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>282042</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>45733; 66020</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>43504; 63886</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>53763; 74796</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>125129; 142927</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>48762; 68061</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>39930; 58357</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>42081; 61717</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>137473; 156234</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>97239; 126625</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>88593; 115647</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>101219; 129351</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>268317; 294115</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1496</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>165636</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>169071</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>179144</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>518745</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>197211</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>189318</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>190343</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>576450</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>362846</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>358388</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>369487</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1095195</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>149513; 182265</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>153090; 187837</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>163082; 198848</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>495054; 541281</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>179082; 213526</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>172586; 208284</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>173316; 207870</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>543841; 602518</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>338020; 386435</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>333641; 385221</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>342393; 393868</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1058540; 1130723</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,22; 35,0</t>
+          <t>21,08; 34,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,46; 44,62</t>
+          <t>27,47; 44,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,62; 41,49</t>
+          <t>25,11; 41,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69,97; 82,57</t>
+          <t>70,2; 82,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,09; 41,18</t>
+          <t>26,39; 40,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,43; 43,24</t>
+          <t>28,22; 43,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,36; 38,32</t>
+          <t>23,25; 39,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,69; 77,67</t>
+          <t>51,59; 77,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,19; 36,31</t>
+          <t>25,8; 35,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,63; 41,2</t>
+          <t>30,58; 41,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26,29; 37,47</t>
+          <t>25,7; 36,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,11; 77,92</t>
+          <t>61,61; 78,33</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,33; 37,61</t>
+          <t>24,44; 37,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,25; 43,91</t>
+          <t>30,3; 44,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,13; 39,93</t>
+          <t>28,43; 39,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64,88; 78,67</t>
+          <t>64,95; 78,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,35; 43,14</t>
+          <t>30,39; 42,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,34; 45,69</t>
+          <t>32,91; 45,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,57; 41,55</t>
+          <t>29,5; 41,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>68,16; 79,6</t>
+          <t>68,54; 79,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,39; 37,83</t>
+          <t>29,58; 38,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,34; 42,84</t>
+          <t>33,59; 42,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,65; 38,63</t>
+          <t>30,38; 38,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>69,32; 78,22</t>
+          <t>68,87; 78,1</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,5; 45,97</t>
+          <t>32,76; 47,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,44; 40,35</t>
+          <t>25,9; 40,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,08; 35,93</t>
+          <t>23,09; 35,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74,94; 88,84</t>
+          <t>74,23; 88,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,52; 49,95</t>
+          <t>35,75; 49,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,06; 41,44</t>
+          <t>27,74; 41,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,78; 40,97</t>
+          <t>27,5; 41,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71,24; 82,94</t>
+          <t>71,19; 82,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35,8; 46,28</t>
+          <t>35,98; 46,09</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,39; 38,33</t>
+          <t>28,48; 38,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27,37; 36,91</t>
+          <t>27,47; 36,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>75,12; 84,65</t>
+          <t>75,06; 84,66</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,66; 39,93</t>
+          <t>27,3; 40,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,8; 43,76</t>
+          <t>29,99; 44,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,23; 44,83</t>
+          <t>31,78; 44,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,5; 85,09</t>
+          <t>74,56; 85,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,07; 43,37</t>
+          <t>31,02; 43,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,77; 37,66</t>
+          <t>25,01; 38,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,6; 39,01</t>
+          <t>26,7; 38,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>75,85; 86,2</t>
+          <t>75,26; 85,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,17; 39,29</t>
+          <t>30,72; 39,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,44; 38,43</t>
+          <t>29,44; 38,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31,14; 39,8</t>
+          <t>30,86; 39,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76,84; 84,23</t>
+          <t>77,01; 84,01</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,7; 36,21</t>
+          <t>29,43; 36,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,1; 39,38</t>
+          <t>32,1; 39,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,04; 37,85</t>
+          <t>30,92; 37,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74,32; 81,25</t>
+          <t>74,28; 81,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,88; 40,4</t>
+          <t>33,95; 40,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,03; 38,66</t>
+          <t>32,02; 38,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,35; 36,4</t>
+          <t>29,68; 36,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>71,37; 79,07</t>
+          <t>71,53; 78,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,76; 37,45</t>
+          <t>32,73; 37,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32,85; 37,92</t>
+          <t>32,81; 37,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31,23; 35,92</t>
+          <t>31,59; 36,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>74,12; 79,18</t>
+          <t>73,79; 78,81</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22327; 36818</t>
+          <t>22183; 36681</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27644; 43336</t>
+          <t>26680; 43409</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22175; 37375</t>
+          <t>22618; 37716</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>82065; 96838</t>
+          <t>82328; 97064</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32042; 48714</t>
+          <t>31215; 48273</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30857; 48647</t>
+          <t>31748; 48999</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23401; 40107</t>
+          <t>24336; 40883</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>72583; 109058</t>
+          <t>72433; 109469</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58541; 81146</t>
+          <t>57661; 80411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64208; 86363</t>
+          <t>64101; 86393</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51208; 72975</t>
+          <t>50057; 71730</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>160056; 200802</t>
+          <t>158766; 201845</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30402; 46995</t>
+          <t>30537; 46393</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39018; 56635</t>
+          <t>39079; 56847</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42742; 60667</t>
+          <t>43190; 60729</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>123606; 149885</t>
+          <t>123733; 150249</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42717; 60718</t>
+          <t>42773; 60345</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49982; 70618</t>
+          <t>50866; 70682</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51840; 72832</t>
+          <t>51717; 72240</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>173820; 203007</t>
+          <t>174801; 203275</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>78087; 100507</t>
+          <t>78600; 102179</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94544; 121478</t>
+          <t>95246; 120370</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>100286; 126408</t>
+          <t>99422; 125874</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>308843; 348504</t>
+          <t>306851; 347958</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35054; 49575</t>
+          <t>35328; 51099</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26672; 42309</t>
+          <t>27155; 41943</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26904; 41883</t>
+          <t>26917; 41561</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>142691; 169159</t>
+          <t>141329; 168869</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>39980; 56231</t>
+          <t>40240; 55911</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31599; 48392</t>
+          <t>32396; 49012</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36903; 54422</t>
+          <t>36532; 54500</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>131998; 153668</t>
+          <t>131912; 153470</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>78909; 102015</t>
+          <t>79312; 101600</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62929; 84960</t>
+          <t>63120; 85201</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68262; 92049</t>
+          <t>68521; 92144</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>282198; 318002</t>
+          <t>281989; 318044</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45733; 66020</t>
+          <t>45141; 66415</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43504; 63886</t>
+          <t>43786; 64264</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53763; 74796</t>
+          <t>53018; 74548</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>125129; 142927</t>
+          <t>125229; 143317</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48762; 68061</t>
+          <t>48677; 67939</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39930; 58357</t>
+          <t>38758; 59118</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42081; 61717</t>
+          <t>42236; 61613</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>137473; 156234</t>
+          <t>136392; 155306</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>97239; 126625</t>
+          <t>99006; 126188</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>88593; 115647</t>
+          <t>88594; 116080</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>101219; 129351</t>
+          <t>100302; 129361</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>268317; 294115</t>
+          <t>268904; 293381</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>149513; 182265</t>
+          <t>148119; 182107</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>153090; 187837</t>
+          <t>153097; 186219</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>163082; 198848</t>
+          <t>162427; 199215</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>495054; 541281</t>
+          <t>494793; 542431</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>179082; 213526</t>
+          <t>179464; 214454</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>172586; 208284</t>
+          <t>172497; 208367</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>173316; 207870</t>
+          <t>169476; 207926</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>543841; 602518</t>
+          <t>545068; 601628</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>338020; 386435</t>
+          <t>337770; 388260</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>333641; 385221</t>
+          <t>333254; 384731</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>342393; 393868</t>
+          <t>346326; 396908</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1058540; 1130723</t>
+          <t>1053870; 1125460</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33,71%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>35,88%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30,33%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>71,57%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>27,8%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>35,67%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>32,88%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>76,84%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>33,71%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>35,88%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30,33%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>74,48%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,08; 34,86</t>
+          <t>26,74; 41,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,47; 44,69</t>
+          <t>28,72; 43,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,11; 41,87</t>
+          <t>23,76; 38,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70,2; 82,76</t>
+          <t>55,45; 80,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,39; 40,81</t>
+          <t>21,04; 35,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,22; 43,55</t>
+          <t>28,33; 44,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,25; 39,06</t>
+          <t>25,14; 41,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,59; 77,96</t>
+          <t>71,31; 83,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,8; 35,98</t>
+          <t>26,03; 36,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,58; 41,21</t>
+          <t>30,1; 41,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,7; 36,83</t>
+          <t>25,63; 37,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61,61; 78,33</t>
+          <t>65,29; 79,41</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>36,8%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>39,08%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>35,34%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>75,78%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>30,75%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>36,57%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>33,78%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>73,55%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>36,8%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>39,08%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>35,34%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>75,86%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,44; 37,12</t>
+          <t>30,04; 43,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,3; 44,07</t>
+          <t>33,44; 46,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,43; 39,97</t>
+          <t>29,49; 40,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64,95; 78,87</t>
+          <t>69,46; 80,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,39; 42,88</t>
+          <t>24,91; 37,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,91; 45,73</t>
+          <t>29,75; 43,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,5; 41,21</t>
+          <t>28,25; 40,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>68,54; 79,7</t>
+          <t>70,58; 81,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,58; 38,46</t>
+          <t>29,21; 38,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,59; 42,45</t>
+          <t>33,57; 42,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,38; 38,47</t>
+          <t>30,76; 38,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>68,87; 78,1</t>
+          <t>71,96; 79,55</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>42,23%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>34,24%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>33,9%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>77,51%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>39,19%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>32,61%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>29,6%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>80,94%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>42,23%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>34,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>33,9%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>77,1%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,76; 47,38</t>
+          <t>34,82; 49,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,9; 40,0</t>
+          <t>27,8; 41,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,09; 35,66</t>
+          <t>26,98; 40,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74,23; 88,69</t>
+          <t>71,46; 83,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,75; 49,67</t>
+          <t>31,82; 46,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,74; 41,97</t>
+          <t>25,63; 40,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,5; 41,02</t>
+          <t>23,57; 36,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71,19; 82,83</t>
+          <t>70,84; 82,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35,98; 46,09</t>
+          <t>35,75; 45,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,48; 38,44</t>
+          <t>28,73; 38,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27,47; 36,95</t>
+          <t>27,48; 36,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>75,06; 84,66</t>
+          <t>72,4; 80,79</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36,95%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>31,34%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>32,62%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>81,88%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>33,69%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>36,35%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>38,18%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>80,01%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>36,95%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>31,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32,62%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,91%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,3; 40,17</t>
+          <t>31,09; 43,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,99; 44,02</t>
+          <t>25,07; 38,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,78; 44,69</t>
+          <t>26,64; 38,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,56; 85,33</t>
+          <t>77,02; 86,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,02; 43,29</t>
+          <t>27,29; 40,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,01; 38,15</t>
+          <t>29,55; 42,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,7; 38,94</t>
+          <t>31,89; 44,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>75,26; 85,69</t>
+          <t>74,15; 85,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,72; 39,15</t>
+          <t>31,03; 39,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,44; 38,57</t>
+          <t>29,34; 38,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,86; 39,8</t>
+          <t>31,15; 39,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,01; 84,01</t>
+          <t>77,4; 84,34</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>37,31%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35,14%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>33,33%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>76,91%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>32,91%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>35,45%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>34,1%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>77,87%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>37,31%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>35,14%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>33,33%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>77,18%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,43; 36,18</t>
+          <t>33,89; 40,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,1; 39,04</t>
+          <t>31,81; 38,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,92; 37,92</t>
+          <t>30,28; 36,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74,28; 81,43</t>
+          <t>73,12; 79,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,95; 40,57</t>
+          <t>29,64; 36,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,02; 38,67</t>
+          <t>31,76; 39,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,68; 36,41</t>
+          <t>30,69; 37,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>71,53; 78,96</t>
+          <t>74,71; 80,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,73; 37,63</t>
+          <t>32,83; 37,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32,81; 37,88</t>
+          <t>32,69; 37,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31,59; 36,2</t>
+          <t>31,33; 36,24</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,79; 78,81</t>
+          <t>74,89; 79,3</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>149</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>39880</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>40360</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>31745</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>90105</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>29244</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>34642</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>29617</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>90123</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>39880</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>40360</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>31745</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>94665</t>
+          <t>93839</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>184789</t>
+          <t>183944</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22183; 36681</t>
+          <t>31631; 49447</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26680; 43409</t>
+          <t>32308; 48747</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22618; 37716</t>
+          <t>24868; 40151</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>82328; 97064</t>
+          <t>69813; 101249</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>31215; 48273</t>
+          <t>22133; 37415</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31748; 48999</t>
+          <t>27518; 42865</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24336; 40883</t>
+          <t>22647; 37648</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>72433; 109469</t>
+          <t>86339; 100682</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>57661; 80411</t>
+          <t>58188; 81421</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64101; 86393</t>
+          <t>63092; 86514</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50057; 71730</t>
+          <t>49914; 72577</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>158766; 201845</t>
+          <t>161254; 196116</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>215</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>51795</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>60402</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>61947</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>179765</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>38430</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>47166</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>51320</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>140114</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>51795</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>60402</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>61947</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>190549</t>
+          <t>140094</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>330664</t>
+          <t>319859</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30537; 46393</t>
+          <t>42274; 60960</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39079; 56847</t>
+          <t>51690; 71191</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43190; 60729</t>
+          <t>51695; 71846</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>123733; 150249</t>
+          <t>164763; 191719</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42773; 60345</t>
+          <t>31134; 47208</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50866; 70682</t>
+          <t>38373; 56435</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51717; 72240</t>
+          <t>42918; 61587</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>174801; 203275</t>
+          <t>130156; 149661</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>78600; 102179</t>
+          <t>77612; 102427</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95246; 120370</t>
+          <t>95191; 121188</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>99422; 125874</t>
+          <t>100647; 126921</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>306851; 347958</t>
+          <t>303414; 335398</t>
         </is>
       </c>
     </row>
@@ -1925,37 +1925,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>57</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>47541</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>39990</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>45038</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>130479</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>42262</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>34194</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>34505</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>154115</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>47541</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>39990</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>45038</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>143586</t>
+          <t>120386</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>297701</t>
+          <t>250865</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35328; 51099</t>
+          <t>39194; 55665</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27155; 41943</t>
+          <t>32464; 48879</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26917; 41561</t>
+          <t>35837; 53627</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>141329; 168869</t>
+          <t>120291; 140452</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>40240; 55911</t>
+          <t>34318; 50324</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32396; 49012</t>
+          <t>26871; 42196</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36532; 54500</t>
+          <t>27474; 42370</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>131912; 153470</t>
+          <t>111250; 129074</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>79312; 101600</t>
+          <t>78805; 100588</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63120; 85201</t>
+          <t>63671; 85062</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68521; 92144</t>
+          <t>68544; 91702</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>281989; 318044</t>
+          <t>235594; 262870</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>193</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>57994</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>48566</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>51612</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>138691</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>55700</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>53069</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>63702</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>134393</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>57994</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>48566</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>51612</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>147649</t>
+          <t>133592</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>282042</t>
+          <t>272283</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45141; 66415</t>
+          <t>48788; 68320</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43786; 64264</t>
+          <t>38851; 59271</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53018; 74548</t>
+          <t>42142; 61489</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>125229; 143317</t>
+          <t>130451; 146701</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48677; 67939</t>
+          <t>45122; 66149</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38758; 59118</t>
+          <t>43143; 62617</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42236; 61613</t>
+          <t>53195; 74535</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>136392; 155306</t>
+          <t>123930; 142545</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>99006; 126188</t>
+          <t>99996; 127708</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>88594; 116080</t>
+          <t>88306; 116072</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>100302; 129361</t>
+          <t>101249; 129645</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>268904; 293381</t>
+          <t>260451; 283821</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>241</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>266</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>731</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>197211</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>189318</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>190343</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>539040</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>165636</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>169071</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>179144</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>518745</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>197211</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>189318</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>190343</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>576450</t>
+          <t>487909</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1095195</t>
+          <t>1026950</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>148119; 182107</t>
+          <t>179147; 213532</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>153097; 186219</t>
+          <t>171369; 208553</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>162427; 199215</t>
+          <t>172936; 210538</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>494793; 542431</t>
+          <t>512446; 559254</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>179464; 214454</t>
+          <t>149198; 182885</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>172497; 208367</t>
+          <t>151473; 186786</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>169476; 207926</t>
+          <t>161254; 195993</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>545068; 601628</t>
+          <t>470432; 505171</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>337770; 388260</t>
+          <t>338740; 388537</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>333254; 384731</t>
+          <t>332062; 381335</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>346326; 396908</t>
+          <t>343486; 397367</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1053870; 1125460</t>
+          <t>996381; 1055093</t>
         </is>
       </c>
     </row>
